--- a/Data Files/Backoffce/IndexacaoFG/Arquivos/Relatório de Recusas  22.09.2025 a 28.09.2025.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/Arquivos/Relatório de Recusas  22.09.2025 a 28.09.2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms.sharepoint.com/teams/BR0010-4356589/Shared Documents/BACK-OFFICE SME/Santander/2025/Relatório de Recusas/05. Maio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{789F15AF-A74B-465C-9554-0E89E2349FE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{54E38425-4CFE-41E5-93BB-7B54F552EE3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19530" windowHeight="9780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19530" windowHeight="9780" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="22.09" sheetId="2" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="77">
   <si>
     <t>SEGURADORA</t>
   </si>
@@ -177,13 +177,118 @@
   </si>
   <si>
     <t>MARCIA CRISTINA BEZERRA SOUSA -CPF 06911915490</t>
+  </si>
+  <si>
+    <t>ELTON MENDES RIBEIRO EVANGELISTA CPF 00156013584</t>
+  </si>
+  <si>
+    <t>Demais Motivos</t>
+  </si>
+  <si>
+    <t>Renovação de outro corretor</t>
+  </si>
+  <si>
+    <t>19/09/2025</t>
+  </si>
+  <si>
+    <t>23/09/2025</t>
+  </si>
+  <si>
+    <t>SANTA BRANCA EXPRESS LTDA ME-30611969000160</t>
+  </si>
+  <si>
+    <t>Chassi irregular, favor corrigir</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANA PAULA VIEIRA DA SILVA                    </t>
+  </si>
+  <si>
+    <t>Duplicidade;</t>
+  </si>
+  <si>
+    <t>Santander - Veículo em duplicidade com proposta </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SELMA CRISTINA BISPO PANTAROTTO              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANTONIA ROBERTA MARTINS                      </t>
+  </si>
+  <si>
+    <t>A pedido do segurado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WALTER SCHMIDT FELSCH JUNIOR                 </t>
+  </si>
+  <si>
+    <t>NUP Cancelamento 22.09.2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AUTOMOTORS SOLUCOES AUTOMOTIVAS LTDA EPP     </t>
+  </si>
+  <si>
+    <t>Conforme consulta na central de bônus, identificamos que não há po
+ssibilidade de efetuar a transferência de bônus para a empresa AUT
+OMOTORS SOLUCOES AUTOMOTIVAS LTDA EP, pois o segurado anterior LUI
+SALVES DE SOUZA não consta no quadro de sócios.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOSE PASCHOAL BATISTUTI                      </t>
+  </si>
+  <si>
+    <t>FRUSTRADA: CLIENTE NÃO CORRIGIU A FOTO INCORRETA - PRAZO EXPIRADO FOTO CORRETA: HODOMETRO.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RENATA MONTEIRO ANTUNES LIMA MUCIDA          </t>
+  </si>
+  <si>
+    <t>Bloqueio recusado devido ao parecer da vistoria prévia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIDIA MATOS DE MELO PANIFICADORA ME          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAPHAEL TEIXEIRA DA SILVA                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SIMONE SANTOS GRANGEIRO                      </t>
+  </si>
+  <si>
+    <t>&gt;Conforme consulta na central de bônus, identificamos que a
+apólice consta ativa na congênere, para que possamos prosseguir
+coma liberação do bloqueio será necessário a apresentação do en
+dosso de cancelamento emitido</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OSIAS RODRIGUES DE SOUZA                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAROLINE CRISTINE GREGORIO RUBINATO          </t>
+  </si>
+  <si>
+    <t>FRUSTRADA: CLIENTE NÃO CORRIGU A FOTO INCORRETA - PRAZO EXPIRADO FOTO INCORRETA: CHASSI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALISSON CORREA BALLESTER                     </t>
+  </si>
+  <si>
+    <t>CLIENTE NÃO CORRIGIU AS FOTOS INCORRETAS - PRAZO EXPIRADO FOTO INCORRETA: MOTOR, CHASSI, PORTA MALAS, HODÔMETRO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROSMEN DOS SANTOS LOPES                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANA CRISTINA DE OLIVEIRA                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DOUGLAS CESAR NEVES DE OLIVEIRA              </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -220,8 +325,22 @@
       <color theme="1"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF414141"/>
+      <name val="Allianz Neo"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -234,8 +353,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="15">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -417,12 +542,27 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -536,13 +676,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -552,12 +685,34 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal_Plan2_1" xfId="1" xr:uid="{69F13A52-20D9-46CA-8619-BC7A1BA09FD8}"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -942,7 +1097,7 @@
       <c r="D2" s="24">
         <v>134355005</v>
       </c>
-      <c r="E2" s="52">
+      <c r="E2" s="47">
         <v>3450073143</v>
       </c>
       <c r="F2" s="12" t="s">
@@ -951,7 +1106,7 @@
       <c r="G2" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="48" t="s">
+      <c r="H2" s="9" t="s">
         <v>12</v>
       </c>
       <c r="I2" s="26">
@@ -971,7 +1126,7 @@
       <c r="D3" s="24">
         <v>134441915</v>
       </c>
-      <c r="E3" s="53">
+      <c r="E3" s="48">
         <v>3450080381</v>
       </c>
       <c r="F3" s="12" t="s">
@@ -1000,7 +1155,7 @@
       <c r="D4" s="24">
         <v>134468232</v>
       </c>
-      <c r="E4" s="53">
+      <c r="E4" s="48">
         <v>3450081360</v>
       </c>
       <c r="F4" s="12" t="s">
@@ -1009,7 +1164,7 @@
       <c r="G4" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="H4" s="48" t="s">
+      <c r="H4" s="9" t="s">
         <v>18</v>
       </c>
       <c r="I4" s="26">
@@ -1029,7 +1184,7 @@
       <c r="D5" s="24">
         <v>134496238</v>
       </c>
-      <c r="E5" s="53">
+      <c r="E5" s="48">
         <v>3450082592</v>
       </c>
       <c r="F5" s="12" t="s">
@@ -1038,7 +1193,7 @@
       <c r="G5" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="H5" s="48" t="s">
+      <c r="H5" s="9" t="s">
         <v>21</v>
       </c>
       <c r="I5" s="26">
@@ -1058,7 +1213,7 @@
       <c r="D6" s="24">
         <v>134500969</v>
       </c>
-      <c r="E6" s="53">
+      <c r="E6" s="48">
         <v>3450082890</v>
       </c>
       <c r="F6" s="12" t="s">
@@ -1067,7 +1222,7 @@
       <c r="G6" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="H6" s="49" t="s">
+      <c r="H6" s="21" t="s">
         <v>21</v>
       </c>
       <c r="I6" s="26">
@@ -1087,7 +1242,7 @@
       <c r="D7" s="24">
         <v>134493095</v>
       </c>
-      <c r="E7" s="53">
+      <c r="E7" s="48">
         <v>3450082394</v>
       </c>
       <c r="F7" s="12" t="s">
@@ -1096,7 +1251,7 @@
       <c r="G7" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="H7" s="50" t="s">
+      <c r="H7" s="12" t="s">
         <v>18</v>
       </c>
       <c r="I7" s="26">
@@ -1116,7 +1271,7 @@
       <c r="D8" s="24">
         <v>134517081</v>
       </c>
-      <c r="E8" s="53">
+      <c r="E8" s="48">
         <v>3450081900</v>
       </c>
       <c r="F8" s="12" t="s">
@@ -1125,7 +1280,7 @@
       <c r="G8" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="H8" s="50" t="s">
+      <c r="H8" s="12" t="s">
         <v>18</v>
       </c>
       <c r="I8" s="26">
@@ -1145,7 +1300,7 @@
       <c r="D9" s="24">
         <v>134521309</v>
       </c>
-      <c r="E9" s="53">
+      <c r="E9" s="48">
         <v>3450082647</v>
       </c>
       <c r="F9" s="12" t="s">
@@ -1154,7 +1309,7 @@
       <c r="G9" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="H9" s="51" t="s">
+      <c r="H9" s="15" t="s">
         <v>21</v>
       </c>
       <c r="I9" s="26">
@@ -1174,7 +1329,7 @@
       <c r="D10" s="24">
         <v>134519081</v>
       </c>
-      <c r="E10" s="53">
+      <c r="E10" s="48">
         <v>3450083868</v>
       </c>
       <c r="F10" s="12" t="s">
@@ -1183,7 +1338,7 @@
       <c r="G10" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="H10" s="48" t="s">
+      <c r="H10" s="9" t="s">
         <v>18</v>
       </c>
       <c r="I10" s="26">
@@ -1203,7 +1358,7 @@
       <c r="D11" s="24">
         <v>134553838</v>
       </c>
-      <c r="E11" s="53">
+      <c r="E11" s="48">
         <v>3450086101</v>
       </c>
       <c r="F11" s="12" t="s">
@@ -1212,7 +1367,7 @@
       <c r="G11" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="H11" s="48" t="s">
+      <c r="H11" s="9" t="s">
         <v>18</v>
       </c>
       <c r="I11" s="26">
@@ -1232,7 +1387,7 @@
       <c r="D12" s="24">
         <v>134419085</v>
       </c>
-      <c r="E12" s="53">
+      <c r="E12" s="48">
         <v>3450078600</v>
       </c>
       <c r="F12" s="12" t="s">
@@ -1261,7 +1416,7 @@
       <c r="D13" s="24">
         <v>134450713</v>
       </c>
-      <c r="E13" s="53">
+      <c r="E13" s="48">
         <v>3450080690</v>
       </c>
       <c r="F13" s="12" t="s">
@@ -1270,7 +1425,7 @@
       <c r="G13" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="H13" s="48" t="s">
+      <c r="H13" s="9" t="s">
         <v>31</v>
       </c>
       <c r="I13" s="26">
@@ -1290,7 +1445,7 @@
       <c r="D14" s="24">
         <v>134420215</v>
       </c>
-      <c r="E14" s="53">
+      <c r="E14" s="48">
         <v>3450079633</v>
       </c>
       <c r="F14" s="12" t="s">
@@ -1319,7 +1474,7 @@
       <c r="D15" s="24">
         <v>134421253</v>
       </c>
-      <c r="E15" s="53">
+      <c r="E15" s="48">
         <v>3450079699</v>
       </c>
       <c r="F15" s="12" t="s">
@@ -1348,7 +1503,7 @@
       <c r="D16" s="24">
         <v>134430120</v>
       </c>
-      <c r="E16" s="53">
+      <c r="E16" s="48">
         <v>3450080007</v>
       </c>
       <c r="F16" s="12" t="s">
@@ -1377,7 +1532,7 @@
       <c r="D17" s="24">
         <v>134380262</v>
       </c>
-      <c r="E17" s="53">
+      <c r="E17" s="48">
         <v>3450077620</v>
       </c>
       <c r="F17" s="12" t="s">
@@ -1406,7 +1561,7 @@
       <c r="D18" s="24">
         <v>134438763</v>
       </c>
-      <c r="E18" s="53">
+      <c r="E18" s="48">
         <v>3450080315</v>
       </c>
       <c r="F18" s="12" t="s">
@@ -1435,7 +1590,7 @@
       <c r="D19" s="24">
         <v>134454618</v>
       </c>
-      <c r="E19" s="53">
+      <c r="E19" s="48">
         <v>3450080898</v>
       </c>
       <c r="F19" s="12" t="s">
@@ -1444,7 +1599,7 @@
       <c r="G19" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="H19" s="48" t="s">
+      <c r="H19" s="9" t="s">
         <v>39</v>
       </c>
       <c r="I19" s="26">
@@ -1457,7 +1612,7 @@
       <c r="C20" s="27"/>
       <c r="D20" s="46"/>
       <c r="E20" s="18"/>
-      <c r="F20" s="54"/>
+      <c r="F20" s="49"/>
       <c r="G20" s="20"/>
       <c r="H20" s="9"/>
       <c r="I20" s="26"/>
@@ -1866,14 +2021,14 @@
   <dimension ref="A1:I55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="16" customWidth="1"/>
+    <col min="1" max="1" width="8.42578125" customWidth="1"/>
     <col min="2" max="2" width="16.5703125" customWidth="1"/>
     <col min="3" max="3" width="21.5703125" customWidth="1"/>
-    <col min="4" max="4" width="27.7109375" style="17" customWidth="1"/>
-    <col min="5" max="5" width="18.5703125" customWidth="1"/>
-    <col min="6" max="6" width="38.28515625" customWidth="1"/>
+    <col min="4" max="4" width="12.85546875" style="17" customWidth="1"/>
+    <col min="5" max="5" width="15.42578125" customWidth="1"/>
+    <col min="6" max="6" width="31" customWidth="1"/>
     <col min="7" max="7" width="19.7109375" customWidth="1"/>
-    <col min="8" max="8" width="24" customWidth="1"/>
+    <col min="8" max="8" width="26" customWidth="1"/>
     <col min="9" max="9" width="22.7109375" style="16" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1906,11 +2061,11 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="23.25">
+    <row r="2" spans="1:9">
       <c r="A2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="7">
+      <c r="B2" s="27">
         <v>45902</v>
       </c>
       <c r="C2" s="27">
@@ -1922,18 +2077,18 @@
       <c r="E2" s="18">
         <v>3450074661</v>
       </c>
-      <c r="F2" s="19" t="s">
+      <c r="F2" s="12" t="s">
         <v>41</v>
       </c>
       <c r="G2" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="H2" s="19" t="s">
+      <c r="H2" s="55" t="s">
         <v>42</v>
       </c>
       <c r="I2" s="26"/>
     </row>
-    <row r="3" spans="1:9" ht="23.25">
+    <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
@@ -1949,13 +2104,13 @@
       <c r="E3" s="18">
         <v>3450084935</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="F3" s="24" t="s">
         <v>43</v>
       </c>
       <c r="G3" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="H3" s="47" t="s">
+      <c r="H3" s="54" t="s">
         <v>42</v>
       </c>
       <c r="I3" s="26"/>
@@ -1964,235 +2119,527 @@
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="27"/>
-      <c r="D4" s="24"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="20"/>
-      <c r="H4" s="9"/>
+      <c r="B4" s="7">
+        <v>45918</v>
+      </c>
+      <c r="C4" s="27">
+        <v>45923</v>
+      </c>
+      <c r="D4" s="50" t="s">
+        <v>40</v>
+      </c>
+      <c r="E4" s="18">
+        <v>3450084528</v>
+      </c>
+      <c r="F4" s="30" t="s">
+        <v>44</v>
+      </c>
+      <c r="G4" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>46</v>
+      </c>
       <c r="I4" s="26"/>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="27"/>
-      <c r="D5" s="24"/>
-      <c r="E5" s="18"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="9"/>
+      <c r="B5" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C5" s="27" t="s">
+        <v>48</v>
+      </c>
+      <c r="D5" s="50" t="s">
+        <v>40</v>
+      </c>
+      <c r="E5" s="51">
+        <v>3450085100</v>
+      </c>
+      <c r="F5" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="G5" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>50</v>
+      </c>
       <c r="I5" s="26"/>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="27"/>
-      <c r="D6" s="24"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="20"/>
-      <c r="H6" s="21"/>
-      <c r="I6" s="26"/>
+      <c r="B6" s="7">
+        <v>45910</v>
+      </c>
+      <c r="C6" s="27" t="s">
+        <v>48</v>
+      </c>
+      <c r="D6" s="24">
+        <v>134379567</v>
+      </c>
+      <c r="E6" s="48">
+        <v>3450077510</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="G6" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="I6" s="7">
+        <v>45910</v>
+      </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="27"/>
-      <c r="D7" s="24"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="25"/>
-      <c r="H7" s="30"/>
-      <c r="I7" s="26"/>
+      <c r="B7" s="7">
+        <v>45915</v>
+      </c>
+      <c r="C7" s="27" t="s">
+        <v>48</v>
+      </c>
+      <c r="D7" s="24">
+        <v>134450716</v>
+      </c>
+      <c r="E7" s="48">
+        <v>3450080700</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="G7" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H7" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="I7" s="7">
+        <v>45915</v>
+      </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="27"/>
-      <c r="D8" s="24"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="25"/>
-      <c r="H8" s="12"/>
-      <c r="I8" s="26"/>
+      <c r="B8" s="7">
+        <v>45916</v>
+      </c>
+      <c r="C8" s="27" t="s">
+        <v>48</v>
+      </c>
+      <c r="D8" s="24">
+        <v>134445901</v>
+      </c>
+      <c r="E8" s="48">
+        <v>3450079754</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="G8" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="H8" s="30" t="s">
+        <v>56</v>
+      </c>
+      <c r="I8" s="26">
+        <v>45919</v>
+      </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="27"/>
-      <c r="D9" s="24"/>
-      <c r="E9" s="18"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="20"/>
-      <c r="H9" s="15"/>
-      <c r="I9" s="26"/>
+      <c r="B9" s="7">
+        <v>45923</v>
+      </c>
+      <c r="C9" s="27" t="s">
+        <v>48</v>
+      </c>
+      <c r="D9" s="24">
+        <v>134498760</v>
+      </c>
+      <c r="E9" s="48">
+        <v>3450082768</v>
+      </c>
+      <c r="F9" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="G9" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="H9" s="56" t="s">
+        <v>58</v>
+      </c>
+      <c r="I9" s="26">
+        <v>45922</v>
+      </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="7"/>
-      <c r="C10" s="27"/>
-      <c r="D10" s="24"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="20"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="26"/>
+      <c r="B10" s="7">
+        <v>45918</v>
+      </c>
+      <c r="C10" s="27" t="s">
+        <v>48</v>
+      </c>
+      <c r="D10" s="24">
+        <v>134516870</v>
+      </c>
+      <c r="E10" s="48">
+        <v>3450083692</v>
+      </c>
+      <c r="F10" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="G10" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="H10" s="52" t="s">
+        <v>60</v>
+      </c>
+      <c r="I10" s="26">
+        <v>45923</v>
+      </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="7"/>
-      <c r="C11" s="27"/>
-      <c r="D11" s="24"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="20"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="26"/>
+      <c r="B11" s="7">
+        <v>45918</v>
+      </c>
+      <c r="C11" s="27" t="s">
+        <v>48</v>
+      </c>
+      <c r="D11" s="24">
+        <v>134529211</v>
+      </c>
+      <c r="E11" s="48">
+        <v>3450084539</v>
+      </c>
+      <c r="F11" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="G11" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="I11" s="26">
+        <v>45918</v>
+      </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="7"/>
-      <c r="C12" s="27"/>
-      <c r="D12" s="24"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="20"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="26"/>
+      <c r="B12" s="7">
+        <v>45922</v>
+      </c>
+      <c r="C12" s="27" t="s">
+        <v>48</v>
+      </c>
+      <c r="D12" s="24">
+        <v>134573678</v>
+      </c>
+      <c r="E12" s="48">
+        <v>3450086651</v>
+      </c>
+      <c r="F12" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="G12" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="I12" s="26">
+        <v>45922</v>
+      </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="7"/>
-      <c r="C13" s="27"/>
-      <c r="D13" s="24"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="20"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="26"/>
+      <c r="B13" s="7">
+        <v>45916</v>
+      </c>
+      <c r="C13" s="27" t="s">
+        <v>48</v>
+      </c>
+      <c r="D13" s="24">
+        <v>134485071</v>
+      </c>
+      <c r="E13" s="48">
+        <v>3450082185</v>
+      </c>
+      <c r="F13" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="G13" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="I13" s="26">
+        <v>45916</v>
+      </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="7"/>
-      <c r="C14" s="27"/>
-      <c r="D14" s="24"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="20"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="26"/>
+      <c r="B14" s="7">
+        <v>45915</v>
+      </c>
+      <c r="C14" s="27" t="s">
+        <v>48</v>
+      </c>
+      <c r="D14" s="24">
+        <v>134446135</v>
+      </c>
+      <c r="E14" s="48">
+        <v>3450080480</v>
+      </c>
+      <c r="F14" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="G14" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="I14" s="26">
+        <v>45919</v>
+      </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="7"/>
-      <c r="C15" s="27"/>
-      <c r="D15" s="24"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="20"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="26"/>
+      <c r="B15" s="7">
+        <v>45910</v>
+      </c>
+      <c r="C15" s="27" t="s">
+        <v>48</v>
+      </c>
+      <c r="D15" s="24">
+        <v>134379980</v>
+      </c>
+      <c r="E15" s="48">
+        <v>3450077587</v>
+      </c>
+      <c r="F15" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="G15" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="H15" s="53" t="s">
+        <v>68</v>
+      </c>
+      <c r="I15" s="26">
+        <v>45915</v>
+      </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B16" s="7"/>
-      <c r="C16" s="27"/>
-      <c r="D16" s="24"/>
-      <c r="E16" s="18"/>
-      <c r="F16" s="12"/>
-      <c r="G16" s="20"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="26"/>
+      <c r="B16" s="7">
+        <v>45910</v>
+      </c>
+      <c r="C16" s="27" t="s">
+        <v>48</v>
+      </c>
+      <c r="D16" s="24">
+        <v>134379871</v>
+      </c>
+      <c r="E16" s="48">
+        <v>3450077576</v>
+      </c>
+      <c r="F16" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="G16" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="I16" s="26">
+        <v>45915</v>
+      </c>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B17" s="7"/>
-      <c r="C17" s="27"/>
-      <c r="D17" s="24"/>
-      <c r="E17" s="18"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="20"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="26"/>
+      <c r="B17" s="7">
+        <v>45918</v>
+      </c>
+      <c r="C17" s="27" t="s">
+        <v>48</v>
+      </c>
+      <c r="D17" s="24">
+        <v>134528375</v>
+      </c>
+      <c r="E17" s="48">
+        <v>3450084473</v>
+      </c>
+      <c r="F17" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="G17" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="I17" s="26">
+        <v>45918</v>
+      </c>
     </row>
     <row r="18" spans="1:9">
-      <c r="A18" s="6"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="27"/>
-      <c r="D18" s="24"/>
-      <c r="E18" s="18"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="20"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="26"/>
+      <c r="A18" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" s="7">
+        <v>45915</v>
+      </c>
+      <c r="C18" s="27" t="s">
+        <v>48</v>
+      </c>
+      <c r="D18" s="24">
+        <v>134461194</v>
+      </c>
+      <c r="E18" s="48">
+        <v>3450081118</v>
+      </c>
+      <c r="F18" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="G18" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="H18" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="I18" s="26">
+        <v>45915</v>
+      </c>
     </row>
     <row r="19" spans="1:9">
-      <c r="A19" s="6"/>
-      <c r="B19" s="7"/>
-      <c r="C19" s="27"/>
-      <c r="D19" s="24"/>
-      <c r="E19" s="18"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="20"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="26"/>
+      <c r="A19" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B19" s="7">
+        <v>45912</v>
+      </c>
+      <c r="C19" s="27" t="s">
+        <v>48</v>
+      </c>
+      <c r="D19" s="24">
+        <v>134446742</v>
+      </c>
+      <c r="E19" s="48">
+        <v>3450079468</v>
+      </c>
+      <c r="F19" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="G19" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="I19" s="26">
+        <v>45912</v>
+      </c>
     </row>
     <row r="20" spans="1:9">
-      <c r="A20" s="6"/>
-      <c r="B20" s="7"/>
-      <c r="C20" s="27"/>
-      <c r="D20" s="24"/>
-      <c r="E20" s="18"/>
-      <c r="F20" s="12"/>
-      <c r="G20" s="20"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="26"/>
+      <c r="A20" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" s="7">
+        <v>45915</v>
+      </c>
+      <c r="C20" s="27" t="s">
+        <v>48</v>
+      </c>
+      <c r="D20" s="24">
+        <v>134453455</v>
+      </c>
+      <c r="E20" s="48">
+        <v>3450080832</v>
+      </c>
+      <c r="F20" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="G20" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H20" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="I20" s="26">
+        <v>45915</v>
+      </c>
     </row>
     <row r="21" spans="1:9">
-      <c r="A21" s="6"/>
-      <c r="B21" s="7"/>
-      <c r="C21" s="27"/>
-      <c r="D21" s="24"/>
-      <c r="E21" s="18"/>
-      <c r="F21" s="12"/>
-      <c r="G21" s="20"/>
-      <c r="H21" s="9"/>
-      <c r="I21" s="26"/>
+      <c r="A21" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B21" s="7">
+        <v>45915</v>
+      </c>
+      <c r="C21" s="27" t="s">
+        <v>48</v>
+      </c>
+      <c r="D21" s="24">
+        <v>134459827</v>
+      </c>
+      <c r="E21" s="48">
+        <v>3450081063</v>
+      </c>
+      <c r="F21" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="G21" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H21" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="I21" s="26">
+        <v>45915</v>
+      </c>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="6"/>
       <c r="B22" s="7"/>
       <c r="C22" s="27"/>
-      <c r="D22" s="24"/>
+      <c r="D22" s="46"/>
       <c r="E22" s="18"/>
-      <c r="F22" s="12"/>
+      <c r="F22" s="35"/>
       <c r="G22" s="20"/>
       <c r="H22" s="9"/>
       <c r="I22" s="26"/>
@@ -2562,9 +3009,12 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:C1">
-    <cfRule type="notContainsBlanks" priority="2">
+    <cfRule type="notContainsBlanks" priority="4">
       <formula>LEN(TRIM(B1))&gt;0</formula>
     </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E5">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A33" xr:uid="{4D257AA8-3FDB-42B7-A450-B3788B0ABB12}">
@@ -5693,58 +6143,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_dlc_DocId xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">QAFFA7D2F2TC-2102087286-496582</_dlc_DocId>
-    <_dlc_DocIdUrl xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Url>https://allianzms.sharepoint.com/teams/BR0010-4356589/_layouts/15/DocIdRedir.aspx?ID=QAFFA7D2F2TC-2102087286-496582</Url>
-      <Description>QAFFA7D2F2TC-2102087286-496582</Description>
-    </_dlc_DocIdUrl>
-    <DossierOwner xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </DossierOwner>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ccca9d190a3c43e89f73773ee806c8b5 xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ccca9d190a3c43e89f73773ee806c8b5>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <ContractDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <MailPreviewData xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <_Flow_SignoffStatus xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ContractExpirationDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <DossierStatus xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <ia4b831ccad64069ad2e0cbd870e9b8a xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ia4b831ccad64069ad2e0cbd870e9b8a>
-    <TaxCatchAll xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <alteradopor xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </alteradopor>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010006E7B04763359F4AAB0FC84D5027BFC8" ma:contentTypeVersion="44" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ac14f8cb44178d381f4c0afb30680a90">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xmlns:ns3="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5e58414b065c9b590c40efa77cd84bb6" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -6122,7 +6520,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
   <Receiver>
@@ -6172,18 +6570,70 @@
 </spe:Receivers>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_dlc_DocId xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">QAFFA7D2F2TC-2102087286-496582</_dlc_DocId>
+    <_dlc_DocIdUrl xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Url>https://allianzms.sharepoint.com/teams/BR0010-4356589/_layouts/15/DocIdRedir.aspx?ID=QAFFA7D2F2TC-2102087286-496582</Url>
+      <Description>QAFFA7D2F2TC-2102087286-496582</Description>
+    </_dlc_DocIdUrl>
+    <DossierOwner xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </DossierOwner>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ccca9d190a3c43e89f73773ee806c8b5 xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ccca9d190a3c43e89f73773ee806c8b5>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <ContractDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <MailPreviewData xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <_Flow_SignoffStatus xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ContractExpirationDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <DossierStatus xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <ia4b831ccad64069ad2e0cbd870e9b8a xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ia4b831ccad64069ad2e0cbd870e9b8a>
+    <TaxCatchAll xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <alteradopor xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </alteradopor>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62AF253E-B31E-4438-928D-DD650DD9CFEA}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13279B2D-D76C-4CA7-B517-83259B9C0FB4}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC9CB02D-0F63-4CE2-B316-61A87327416C}"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C48653D8-7562-408C-9B57-D83FFA71DB43}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{11C2A825-3E96-4907-B2FC-D50A353DAE9F}"/>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13279B2D-D76C-4CA7-B517-83259B9C0FB4}"/>
 </file>